--- a/data/kz/niches/niche_formats_BARBER.xlsx
+++ b/data/kz/niches/niche_formats_BARBER.xlsx
@@ -502,6 +502,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -595,7 +596,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -645,12 +646,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -700,12 +701,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -755,12 +756,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -810,12 +811,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -890,6 +891,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -945,12 +947,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -983,12 +985,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1021,12 +1023,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1059,12 +1061,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1097,12 +1099,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1167,6 +1169,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1217,12 +1220,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1254,12 +1257,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1291,12 +1294,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1328,12 +1331,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1400,6 +1403,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1499,6 +1503,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1813,6 +1818,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1965,6 +1971,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2050,7 +2057,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2104,12 +2111,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2163,12 +2170,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2222,12 +2229,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2281,12 +2288,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2386,6 +2393,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2511,7 +2519,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -2581,12 +2589,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -2656,12 +2664,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -2731,12 +2739,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -2806,12 +2814,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -2917,6 +2925,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2992,7 +3001,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -3034,12 +3043,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -3077,12 +3086,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -3120,12 +3129,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3163,12 +3172,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -3242,6 +3251,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3317,7 +3327,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -3357,12 +3367,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -3402,12 +3412,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -3447,12 +3457,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -3492,12 +3502,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -3570,6 +3580,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3630,7 +3641,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3667,12 +3678,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -3709,12 +3720,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3751,12 +3762,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -3793,12 +3804,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -3871,6 +3882,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3946,7 +3958,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -4002,12 +4014,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -4063,12 +4075,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BARBER_MINI</t>
+          <t>BARBER_STANDARD</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>стандарт</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -4124,12 +4136,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -4185,12 +4197,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -4277,6 +4289,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4327,7 +4340,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
@@ -4361,7 +4374,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -4395,7 +4408,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
@@ -4429,7 +4442,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Эконом</t>
+          <t>эконом</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -4485,6 +4498,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -4510,12 +4524,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -4532,12 +4546,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -4554,12 +4568,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -4576,12 +4590,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>BARBER_FULL</t>
+          <t>BARBER_PREMIUM</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Стандарт</t>
+          <t>премиум</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
